--- a/daily_matches/job_matches_2026-05-28.xlsx
+++ b/daily_matches/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Senior Cloud Engineer - AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Great American Insurance Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, PostgreSQL</t>
+          <t>RAG, AWS SageMaker, S3, Glue, Athena, Kinesis, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+          <t>https://www.indeed.com/viewjob?jk=84652629b44e36b8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Remote</t>
+          <t>Senior AI Engineer- Application Development</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8c49335daa6a23</t>
+          <t>https://www.indeed.com/viewjob?jk=399227e084d1df1f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, MongoDB</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a29d0256393717</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b1236c1664077</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a23763abe2ce85</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69247dcb2f6bbf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer (Full Stack)</t>
+          <t>Apps Dev Analyst-Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carlisle Construction Materials</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carlisle, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Snowflake, Kafka, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6fcd895e0ef228a</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Integrity Marketing Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, Redshift, Git, Redshift, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, Snowflake, PySpark, Dask, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7c692dd6d79196</t>
+          <t>https://www.indeed.com/viewjob?jk=ad459674cc4aabaf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analyst V (6183)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976fd8b03cd8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=9850f114dd4042e0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer -AI/Agentic Systems</t>
+          <t>Sr. Marketing Intelligence Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Copilot, S3, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc98caf56d3e44c</t>
+          <t>https://www.indeed.com/viewjob?jk=89cac26488786d62</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior Network Automation Engineer</t>
+          <t>Data and Analytics - AI Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GTT Communications</t>
+          <t>WoodmenLife</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fe1d7e8218dbdbd</t>
+          <t>https://www.indeed.com/viewjob?jk=562e88c9fb8d5b69</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Data and Analytics - AI Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GTT Communications</t>
+          <t>WoodmenLife</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,392 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcfd614804876c56</t>
+          <t>https://www.indeed.com/viewjob?jk=47927deab443e675</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, Terraform, Snowflake, Databricks, BigQuery, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62f42ce9d9df9845</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Extreme Engineering Solutions</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Verona, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd1c4607dc64c65c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer, AI Platform</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eee9f0ea41c7fa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Junior DevOps Engineer, AI Platform</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a73266d2d7d833b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, CI/CD, Git, Snowflake, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JELLYFISH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, AKS, Terraform, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad25009ecdb4b08c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Analyst - Data Engineering 5A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7f357fe23d7d94f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Just Appraised</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f430dbb7322bcb60</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Verisk</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Holmdel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fed57cf49110e04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Warehouse Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Revinate</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c68680798d8c66f</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Apache Airflow, Git, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=340166e3c8758c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a8edf96943e2589</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-28.xlsx
+++ b/daily_matches/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - AWS</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, Glue, Athena, Kinesis, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>Generative AI, Redshift, Data Lake, Docker, CI/CD, Jenkins, Git, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84652629b44e36b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff822c60b8aee53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer- Application Development</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, S3, Redshift, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399227e084d1df1f</t>
+          <t>https://www.indeed.com/viewjob?jk=28b17aa00b0fc706</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>R&amp;T Software Engineer 3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>Safan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Snowflake, Databricks</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, S3, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b1236c1664077</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3e2857ffc20efe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, spaCy, NLTK, OpenCV, Gensim, S3, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69247dcb2f6bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=53938f65e1e5f649</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Apps Dev Analyst-Cloud Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Snowflake, Kafka, Tableau, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Cortex, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,277 +636,277 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Integrity Marketing Group</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Snowflake, PySpark, Dask, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad459674cc4aabaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8d57d01762e734</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9850f114dd4042e0</t>
+          <t>https://www.indeed.com/viewjob?jk=918547ff5cec5eaf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Marketing Intelligence Analyst</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cac26488786d62</t>
+          <t>https://www.indeed.com/viewjob?jk=fc700a31a9e9384e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data and Analytics - AI Engineer II</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WoodmenLife</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562e88c9fb8d5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e4e871610324c2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data and Analytics - AI Engineer II</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WoodmenLife</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47927deab443e675</t>
+          <t>https://www.indeed.com/viewjob?jk=41464fdd05286b89</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Terraform, Snowflake, Databricks, BigQuery, PySpark, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f42ce9d9df9845</t>
+          <t>https://www.indeed.com/viewjob?jk=beb360aa478ac39e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Extreme Engineering Solutions</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verona, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1c4607dc64c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c29cee9163d5c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Cortex, BigQuery, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eee9f0ea41c7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer, AI Platform</t>
+          <t>Sr AI/Agentic Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Lendistry</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73266d2d7d833b4</t>
+          <t>https://www.indeed.com/viewjob?jk=21637d5634b5c986</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr AI/Agentic Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Lendistry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, Git, Snowflake, Hadoop, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfbb31dbde58387</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr AI/Agentic Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Lendistry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, AKS, Terraform, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad25009ecdb4b08c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc7d4e3421b9fa3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Sr AI/Agentic Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Lendistry</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f357fe23d7d94f</t>
+          <t>https://www.indeed.com/viewjob?jk=542c8ebf33f80b16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr AI/Agentic Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Just Appraised</t>
+          <t>Lendistry</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f430dbb7322bcb60</t>
+          <t>https://www.indeed.com/viewjob?jk=181b2a3255316455</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fed57cf49110e04</t>
+          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Cloud DevOps Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Revinate</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, Git, BigQuery, Kafka, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,1652 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340166e3c8758c46</t>
+          <t>https://www.indeed.com/viewjob?jk=3b704942f95cf9c7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>RedWeek.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Strategic Healthcare Programs</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Goleta, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, PyTorch, XGBoost, MLflow, FastAPI, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ff3b4d89db55394</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec5496e15369abf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24294ee46ae8346d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SWBC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, S3, MLflow, CI/CD, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29eba7528027bc06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5e3cd8fa1790e11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Insperity</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Redshift, Synapse, Snowflake, Databricks, Redshift</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=355ab72b40c4f86b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Associated Press</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, EC2, FastAPI, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8f3939e0fe278ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Associate MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BlueCross BlueShield of Tennessee</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Systems Engineer II</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sinch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde6c60830133d79</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Development Engineer III - Backend</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf0b7804f4424986</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SWBC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, S3, MLflow, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5aa48e97cf417357</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Solution Architect - Agentic AI &amp; Data</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583d17ff8d959f70</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Search Relevance</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, Terraform, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer – Platform Systems (Backend)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Terzo Enterprises</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=016bba447faebcb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Diagonal Matrix Ltd</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Git, Hadoop, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f987c5eb900085be</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DTE Energy</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Azure ML, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6749ff86086e830c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Metronet</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, PySpark, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brentwood, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5878ef5635057786</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Omada Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36467b92bc7ade4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Fullstack Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>turing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0400bdbcd3245745</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, AWS SageMaker, S3, EC2, Glue, CI/CD, Jenkins, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60a519efb7bfbc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Associate Research Scientist (Weiss Lab)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Matplotlib, Seaborn, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4663f6238ac7b84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Applied AI Scientist III</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2544b70954713f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Marketing Ops AI Agent Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Saviynt</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, Git, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7deaa8446a0c162</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full-Stack</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EPIC Kids</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer / Data Integration Specialist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ASSYST, Inc.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6b4d9245e526c87</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics (CWAN)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Birdeye</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Snowflake, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69d838df558801ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HSO Group B.V.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cb4b8268311daa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HSO Group B.V.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481d6a11b777b1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HSO Group B.V.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f255f903515ea9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HSO Group B.V.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88b6fb256069933a</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HSO Group B.V.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e1e99cb580844a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HSO Group B.V.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>Columbus, OH, US USA</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D59" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8edf96943e2589</t>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35897f8634972350</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HSO Group B.V.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dae0b995c82f259d</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MuleSoft Sr Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Kafka, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bfdb65d0a4f474d</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8098af2c43070fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22397dd919c59439</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Engineer (Contractor)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RE/SPEC Inc</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cortex, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7efc11adef097d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineer (173490)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef974492224d6082</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data Engineer (173541)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=129685a2247abc31</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>The Associated Press</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35f187f0bb9f0c0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54882c1908bfa1b4</t>
         </is>
       </c>
     </row>
